--- a/outputs/result.xlsx
+++ b/outputs/result.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.77734375" customWidth="1" min="4" max="4"/>
@@ -481,19 +481,19 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>477.3</v>
+        <v>476.5</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>478.8</v>
+        <v>477</v>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
@@ -511,19 +511,19 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>477.3</v>
+        <v>477.4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>478.8</v>
+        <v>477.9</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -557,19 +557,19 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>477.3</v>
+        <v>481.7</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>478.8</v>
+        <v>482.2</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1</v>
@@ -597,19 +597,19 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>477.5</v>
+        <v>488.6</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>479</v>
+        <v>489.1</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -623,19 +623,19 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>477.5</v>
+        <v>494.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>479</v>
+        <v>495.1</v>
       </c>
     </row>
     <row r="7">
@@ -644,19 +644,19 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>477.5</v>
+        <v>507.8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>479</v>
+        <v>508.3</v>
       </c>
     </row>
     <row r="8">
@@ -665,7 +665,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>508.4</v>
+        <v>513.8</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>509.9</v>
+        <v>515.3</v>
       </c>
     </row>
     <row r="9">
@@ -686,7 +686,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>508.7</v>
+        <v>750.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>509.2</v>
+        <v>750.8</v>
       </c>
     </row>
     <row r="10">
@@ -707,19 +707,19 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>模拟射击</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>508.7</v>
+        <v>751</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>509.2</v>
+        <v>752.5</v>
       </c>
     </row>
     <row r="11">
@@ -728,7 +728,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -737,34 +737,13 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>509</v>
+        <v>762</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>510.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>模拟射击</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>764.9</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>766.4</v>
-      </c>
-    </row>
-    <row r="13"/>
+        <v>763.5</v>
+      </c>
+    </row>
+    <row r="12"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/outputs/result.xlsx
+++ b/outputs/result.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.77734375" customWidth="1" min="4" max="4"/>
@@ -481,19 +481,19 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>477.3</v>
+        <v>476.5</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>478.8</v>
+        <v>477</v>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
@@ -511,19 +511,19 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>477.3</v>
+        <v>477.4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>478.8</v>
+        <v>477.9</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -557,19 +557,19 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>S06</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>477.3</v>
+        <v>481.7</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>478.8</v>
+        <v>482.2</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1</v>
@@ -597,19 +597,19 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>P01</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>477.5</v>
+        <v>488.6</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>479</v>
+        <v>489.1</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
@@ -623,19 +623,19 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>P04</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>477.5</v>
+        <v>494.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>479</v>
+        <v>495.1</v>
       </c>
     </row>
     <row r="7">
@@ -644,19 +644,19 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>模拟射击</t>
+          <t>拍照</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>477.5</v>
+        <v>507.8</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>479</v>
+        <v>508.3</v>
       </c>
     </row>
     <row r="8">
@@ -665,7 +665,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>508.4</v>
+        <v>513.8</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>509.9</v>
+        <v>515.3</v>
       </c>
     </row>
     <row r="9">
@@ -686,7 +686,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>508.7</v>
+        <v>750.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>509.2</v>
+        <v>750.8</v>
       </c>
     </row>
     <row r="10">
@@ -707,19 +707,19 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>拍照</t>
+          <t>模拟射击</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>508.7</v>
+        <v>751</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>509.2</v>
+        <v>752.5</v>
       </c>
     </row>
     <row r="11">
@@ -728,7 +728,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -737,34 +737,13 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>509</v>
+        <v>762</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>510.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>S12</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>模拟射击</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>764.9</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>766.4</v>
-      </c>
-    </row>
-    <row r="13"/>
+        <v>763.5</v>
+      </c>
+    </row>
+    <row r="12"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
